--- a/data/google_news_dedup_audit_22_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_22_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,526 +445,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8054920434951782</v>
+        <v>0.9766607880592346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amazon launches national GLP-1 weight loss management program - Chain Store Age</t>
+          <t>Verdacht pakket ontdekt in wagon: treinverkeer op twee sporen in Brussel-Centraal ligt ruim halfuur stil - HLN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon launches GLP-1 weight loss program integration - tickernews.co</t>
+          <t>Verdacht pakket ontdekt in wagon: treinverkeer op twee sporen in Brussel-Centraal ligt ruim halfuur stil | Foto - HLN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8015918731689453</v>
+        <v>0.8741841912269592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FedEx and IIT Madras complete Bengaluru drone delivery trial, explore future of urban logistics - Storyboard18</t>
+          <t>Kamel Daoud annonce avoir écopé de trois ans de prison en Algérie pour «Houris» - Le Devoir</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FedEx Drone Delivery Trials Complete in Bengaluru - Rediff MoneyWiz</t>
+          <t>Kamel Daoud annonce avoir été condamné à trois ans de prison ferme en Algérie pour son roman «Houris - RFI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>0.832186222076416</v>
+        <v>0.7174684405326843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FedEx and IIT Madras complete Bengaluru drone delivery trial, explore future of urban logistics - Storyboard18</t>
+          <t>Polizei stoppt Autofahrer mit 1,5 Promille und ohne Führerschein - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FedEx conducts India's first intra-city drone delivery trials in Bengaluru - Mint</t>
+          <t>Ingolstadt: Frau kollidiert mit Hund und stürzt – Halter angezeigt - Augsburger Allgemeine</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7000364065170288</v>
+        <v>0.8362529277801514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Verdacht pakket op trein veroorzaakt hinder in Brussel-Centraal - BRUZZ</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Verdacht pakket in Brussel Centraal blijkt onschadelijk te zijn - MSN</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9758692383766174</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Verdacht pakket ontdekt in wagon: treinverkeer op twee sporen in Brussel-Centraal ligt dik halfuur stil - HLN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Verdacht pakket ontdekt in wagon: treinverkeer op twee sporen in Brussel-Centraal ligt dik halfuur stil | Foto - HLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B7" t="n">
-        <v>24</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9980850219726562</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Video: EOD ruimt kruitresten op bij Hoge Weerd in Maastricht - De Limburger</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Video: EOD ruimt kruidresten op bij Hoge Weerd in Maastricht - De Limburger</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B8" t="n">
-        <v>31</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.758830189704895</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Video: EOD ruimt kruitresten op bij Hoge Weerd in Maastricht - De Limburger</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EOD ruimt kruidresten op in Maastricht - De Limburger</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B9" t="n">
-        <v>27</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7512423992156982</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Politie treft jachtgeweer aan bij huiszoeking voor drugshandel in Schaarbeek - BRUZZ</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Twee verdachten ingerekend voor drugsverkoop in Schaarbeek - Nieuwsblad</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B10" t="n">
-        <v>35</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.8650110363960266</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Steekpartij in Hoensbroek, slachtoffer ernstig gewond - De Limburger</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Steekpartij in Hoensbroek: man overleden - De Limburger</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7130355834960938</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>EU Expresses Solidarity with India on Pahalgam Anniversary - The Avenue Mail</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Terror can never be justified: EU expresses solidarity with India on Pahalgam attack anniversary - Social News XYZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>64</v>
-      </c>
-      <c r="B12" t="n">
-        <v>65</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8474823236465454</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Patro Eisden U21 Fixtures and Upcoming Games - Futbol24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Patro Eisden U21 Standings, Matches and Scores - Futbol24</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>73</v>
-      </c>
-      <c r="B13" t="n">
-        <v>75</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.8037238717079163</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Men guilty of church drive-by shooting murder - BBC</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Two men guilty of murdering woman in drive-by shooting at London church - The Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>73</v>
-      </c>
-      <c r="B14" t="n">
-        <v>85</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.6006160378456116</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Men guilty of church drive-by shooting murder - BBC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Two convicted of fatal drive-by shooting of mother outside north London church - London Evening Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>77</v>
-      </c>
-      <c r="B15" t="n">
-        <v>83</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.7183234095573425</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>London Stock Exchange bomb plotter was allowed to stay in UK on human rights grounds - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Terrorist who planned to bomb London Stock Exchange was allowed to stay in UK - The Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>78</v>
-      </c>
-      <c r="B16" t="n">
-        <v>87</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.8280372619628906</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bromley double stabbing leaves man, in 40s, with potentially life-changing injuries - My London</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Arrest made as man left with life-changing injuries after Bromley double stabbing - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>80</v>
-      </c>
-      <c r="B17" t="n">
-        <v>84</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.7064055204391479</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Men arrested after double stabbing at park - London Now</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Two men rushed to hospital after early morning stabbing at park - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>93</v>
-      </c>
-      <c r="B18" t="n">
-        <v>96</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6602616310119629</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>London Tube Strike Set to Cause Travel Chaos for Commuters - Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>London tube strike and the Victoria Line, Tuesday 21st April 2026 – status updates - Brixton Buzz</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>93</v>
-      </c>
-      <c r="B19" t="n">
-        <v>98</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7012181878089905</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>London Tube Strike Set to Cause Travel Chaos for Commuters - Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Tube strike weather boost for thousands of Londoners taking to bikes - London Evening Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>93</v>
-      </c>
-      <c r="B20" t="n">
-        <v>101</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7179547548294067</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>London Tube Strike Set to Cause Travel Chaos for Commuters - Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>10 Tube lines hit by delays and suspensions as strike disruption grips London early - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>93</v>
-      </c>
-      <c r="B21" t="n">
-        <v>103</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.7044439315795898</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>London Tube Strike Set to Cause Travel Chaos for Commuters - Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>London tube strikes: All the dates and underground lines affected by disruption - The Independent</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>104</v>
-      </c>
-      <c r="B22" t="n">
-        <v>111</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.7071709632873535</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Metrotranvia Milano-Seregno: cantieri fermi, cittadini esasperati e scatta la protesta - MonzaToday</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Gemellaggio Milano-Tel Aviv, la protesta in consiglio comunale - Radio Lombardia</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>105</v>
-      </c>
-      <c r="B23" t="n">
-        <v>109</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.7376174330711365</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Sciopero a sorpresa all’hotel Rosa Grand di Milano - cub.it</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Milano, presidio della Cub all'Hotel Rosa Grand: ”Aumentate i ticket dei facchini a 10€ al giorno” - milanopavia.news</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>106</v>
-      </c>
-      <c r="B24" t="n">
-        <v>110</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.7011139392852783</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sciopero trasporti a Milano: orari e fasce di garanzia per il 24 aprile - Milano Post</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MILANO | MANIFESTAZIONE DELLA LEGA, DREOSTO: «EUROPA TROPPO RIGIDA, CI STA PENALIZZANDO» - tv12 medianordest</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>106</v>
-      </c>
-      <c r="B25" t="n">
-        <v>113</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.7761344909667969</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Sciopero trasporti a Milano: orari e fasce di garanzia per il 24 aprile - Milano Post</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Sciopero ATM di 8 ore: guida completa alle fasce di garanzia - Milano Weekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>106</v>
-      </c>
-      <c r="B26" t="n">
-        <v>116</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.7595385313034058</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Sciopero trasporti a Milano: orari e fasce di garanzia per il 24 aprile - Milano Post</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>25 aprile 2026 a Milano: il programma del corteo e gli orari della manifestazione - Milano Pocket</t>
+          <t>Sciopero 24 aprile 2026, a Milano a rischio metro, bus e tram: orari, motivazioni, cosa sapere - Il Giorno</t>
         </is>
       </c>
     </row>

--- a/data/google_news_dedup_audit_22_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_22_0426_UTC.xlsx
@@ -448,10 +448,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9766607880592346</v>
+        <v>0.9766607284545898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -466,13 +466,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8741841912269592</v>
+        <v>0.8741840124130249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -487,10 +487,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
         <v>0.7174684405326843</v>
@@ -508,13 +508,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8362529277801514</v>
+        <v>0.836252748966217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
